--- a/nominas_persistentes.xlsx
+++ b/nominas_persistentes.xlsx
@@ -1,43 +1,286 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="80">
+  <si>
+    <t>DNI</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Vigencia Desde</t>
+  </si>
+  <si>
+    <t>Vigencia Hasta</t>
+  </si>
+  <si>
+    <t>40490370</t>
+  </si>
+  <si>
+    <t>36405261</t>
+  </si>
+  <si>
+    <t>28680171</t>
+  </si>
+  <si>
+    <t>46425429</t>
+  </si>
+  <si>
+    <t>42094381</t>
+  </si>
+  <si>
+    <t>43405376</t>
+  </si>
+  <si>
+    <t>36943401</t>
+  </si>
+  <si>
+    <t>47944022</t>
+  </si>
+  <si>
+    <t>40492015</t>
+  </si>
+  <si>
+    <t>33348064</t>
+  </si>
+  <si>
+    <t>33614626</t>
+  </si>
+  <si>
+    <t>24229383</t>
+  </si>
+  <si>
+    <t>31032804</t>
+  </si>
+  <si>
+    <t>31891299</t>
+  </si>
+  <si>
+    <t>39560013</t>
+  </si>
+  <si>
+    <t>36883797</t>
+  </si>
+  <si>
+    <t>35123007</t>
+  </si>
+  <si>
+    <t>28974205</t>
+  </si>
+  <si>
+    <t>22481988</t>
+  </si>
+  <si>
+    <t>38660601</t>
+  </si>
+  <si>
+    <t>40428609</t>
+  </si>
+  <si>
+    <t>23155256</t>
+  </si>
+  <si>
+    <t>96442771</t>
+  </si>
+  <si>
+    <t>39186037</t>
+  </si>
+  <si>
+    <t>25232046</t>
+  </si>
+  <si>
+    <t>AVALOS ABEL</t>
+  </si>
+  <si>
+    <t>AVALOS EDUARDO</t>
+  </si>
+  <si>
+    <t>AVILA CHRISTIAN</t>
+  </si>
+  <si>
+    <t>AVILA LAUTARO</t>
+  </si>
+  <si>
+    <t>AVILA MARCELO</t>
+  </si>
+  <si>
+    <t>BENITEZ EMILIANO</t>
+  </si>
+  <si>
+    <t>BRITEZ VICTOR</t>
+  </si>
+  <si>
+    <t>BRUNA IGNACIO</t>
+  </si>
+  <si>
+    <t>BUCARI</t>
+  </si>
+  <si>
+    <t>CABAÑA DIEGO</t>
+  </si>
+  <si>
+    <t>CORDERO VICTOR</t>
+  </si>
+  <si>
+    <t>GOMEZ RODRIGO</t>
+  </si>
+  <si>
+    <t>GUEVARA HERMINIO</t>
+  </si>
+  <si>
+    <t>LENCINA FACUNDO</t>
+  </si>
+  <si>
+    <t>LOPEZ RAUWOLF</t>
+  </si>
+  <si>
+    <t>OCAMPO EUGENIO</t>
+  </si>
+  <si>
+    <t>ORDOÑEZ CLAUDIO</t>
+  </si>
+  <si>
+    <t>PEREYRA RODOLFO</t>
+  </si>
+  <si>
+    <t>SANCHEZ LUIS</t>
+  </si>
+  <si>
+    <t>SANIN SANTIAGO</t>
+  </si>
+  <si>
+    <t>SOSA ALAN</t>
+  </si>
+  <si>
+    <t>SOSA FRANCISCO</t>
+  </si>
+  <si>
+    <t>TURMERO ELIO</t>
+  </si>
+  <si>
+    <t>VERRASTRO IAN</t>
+  </si>
+  <si>
+    <t>ZALAZAR ALFREDO</t>
+  </si>
+  <si>
+    <t>ISAIAS</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>FEDERICO</t>
+  </si>
+  <si>
+    <t>MAXIMILIANO</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>SEBASTIAN</t>
+  </si>
+  <si>
+    <t>TOMAS</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>HERNAN</t>
+  </si>
+  <si>
+    <t>WALTER MARCIAL</t>
+  </si>
+  <si>
+    <t>FACUNDO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ALCIDES</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>EMANUEL</t>
+  </si>
+  <si>
+    <t>NICOLAS</t>
+  </si>
+  <si>
+    <t>AURELIO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BUCARI / Adidas</t>
+  </si>
+  <si>
+    <t>Bucari / Adidas</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +288,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,47 +588,1031 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Apellido</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Vigencia Desde</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Vigencia Hasta</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>40490370</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>36405261</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>28680171</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F4" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>46425429</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>42094381</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F6" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>43405376</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>36943401</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F8" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>47944022</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F9" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>40492015</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F10" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>33348064</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>33614626</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>24229383</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F13" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>31032804</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>31891299</v>
+      </c>
+      <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>39560013</v>
+      </c>
+      <c r="B16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>36883797</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>35123007</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>28974205</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F19" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>22481988</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F20" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>38660601</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F21" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>40428609</v>
+      </c>
+      <c r="B22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F22" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>23155256</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>96442771</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F24" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>39186037</v>
+      </c>
+      <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F25" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>25232046</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F28" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F29" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F31" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F32" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F33" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F34" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F35" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F36" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F37" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>43</v>
+      </c>
+      <c r="C39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F40" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F41" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F42" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>69</v>
+      </c>
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F43" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F44" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D45" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F45" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C46" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F46" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F47" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F48" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" t="s">
+        <v>75</v>
+      </c>
+      <c r="D49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F49" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>29</v>
+      </c>
+      <c r="B50" t="s">
+        <v>54</v>
+      </c>
+      <c r="C50" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F50" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="1">
+        <v>46295</v>
+      </c>
+      <c r="F51" s="1">
+        <v>46310</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>